--- a/resources/templates/standard/F2100-05-02.xlsx
+++ b/resources/templates/standard/F2100-05-02.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>자격인증 이론평가 (1)</t>
   </si>
@@ -900,11 +903,13 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
+      <c r="B2" s="6" t="s">
+        <v>0</v>
+      </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -927,7 +932,7 @@
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA2" s="8"/>
       <c r="AB2" s="8"/>
@@ -966,7 +971,7 @@
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA3" s="11"/>
       <c r="AB3" s="11"/>
@@ -1055,7 +1060,7 @@
     <row r="6" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="13" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -1067,7 +1072,7 @@
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
       <c r="L6" s="13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6" s="13"/>
       <c r="N6" s="13"/>
@@ -1079,7 +1084,7 @@
       <c r="T6" s="15"/>
       <c r="U6" s="15"/>
       <c r="V6" s="13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
@@ -1135,7 +1140,7 @@
     <row r="8" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -1167,7 +1172,7 @@
       <c r="AD8" s="12"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG8" s="16"/>
       <c r="AH8" s="16"/>
@@ -1176,7 +1181,7 @@
     <row r="9" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -1217,7 +1222,7 @@
     <row r="10" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1256,7 +1261,7 @@
     <row r="11" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -1295,7 +1300,7 @@
     <row r="12" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1371,7 +1376,7 @@
     <row r="14" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -1403,7 +1408,7 @@
       <c r="AD14" s="12"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG14" s="16"/>
       <c r="AH14" s="16"/>
@@ -1412,7 +1417,7 @@
     <row r="15" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1453,7 +1458,7 @@
     <row r="16" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -1492,7 +1497,7 @@
     <row r="17" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -1531,7 +1536,7 @@
     <row r="18" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -1607,7 +1612,7 @@
     <row r="20" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -1639,7 +1644,7 @@
       <c r="AD20" s="12"/>
       <c r="AE20" s="4"/>
       <c r="AF20" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG20" s="16"/>
       <c r="AH20" s="16"/>
@@ -1648,7 +1653,7 @@
     <row r="21" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -1689,7 +1694,7 @@
     <row r="22" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -1728,7 +1733,7 @@
     <row r="23" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -1767,7 +1772,7 @@
     <row r="24" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -1843,7 +1848,7 @@
     <row r="26" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -1875,7 +1880,7 @@
       <c r="AD26" s="12"/>
       <c r="AE26" s="4"/>
       <c r="AF26" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG26" s="16"/>
       <c r="AH26" s="16"/>
@@ -1884,7 +1889,7 @@
     <row r="27" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -1925,7 +1930,7 @@
     <row r="28" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -1964,7 +1969,7 @@
     <row r="29" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -2003,7 +2008,7 @@
     <row r="30" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -2079,7 +2084,7 @@
     <row r="32" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -2111,7 +2116,7 @@
       <c r="AD32" s="12"/>
       <c r="AE32" s="4"/>
       <c r="AF32" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG32" s="16"/>
       <c r="AH32" s="16"/>
@@ -2120,7 +2125,7 @@
     <row r="33" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -2161,7 +2166,7 @@
     <row r="34" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -2200,7 +2205,7 @@
     <row r="35" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -2239,7 +2244,7 @@
     <row r="36" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -2315,7 +2320,7 @@
     <row r="38" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
       <c r="B38" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -2347,7 +2352,7 @@
       <c r="AD38" s="12"/>
       <c r="AE38" s="4"/>
       <c r="AF38" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG38" s="16"/>
       <c r="AH38" s="16"/>
@@ -2356,7 +2361,7 @@
     <row r="39" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -2397,7 +2402,7 @@
     <row r="40" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -2436,7 +2441,7 @@
     <row r="41" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -2475,7 +2480,7 @@
     <row r="42" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
       <c r="B42" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -2591,7 +2596,7 @@
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F45" s="21"/>
       <c r="G45" s="21"/>
@@ -2738,7 +2743,7 @@
     <row r="49" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
       <c r="B49" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C49" s="17"/>
       <c r="D49" s="17"/>
@@ -2770,7 +2775,7 @@
       <c r="AD49" s="12"/>
       <c r="AE49" s="4"/>
       <c r="AF49" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG49" s="16"/>
       <c r="AH49" s="16"/>
@@ -2779,7 +2784,7 @@
     <row r="50" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
       <c r="B50" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="17"/>
@@ -2788,10 +2793,10 @@
       <c r="G50" s="17"/>
       <c r="H50" s="17"/>
       <c r="I50" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="17"/>
@@ -2815,7 +2820,7 @@
       <c r="AD50" s="12"/>
       <c r="AE50" s="4"/>
       <c r="AF50" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AG50" s="22"/>
       <c r="AH50" s="22"/>
@@ -2832,7 +2837,7 @@
       <c r="H51" s="17"/>
       <c r="I51" s="10"/>
       <c r="J51" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
@@ -2863,7 +2868,7 @@
     <row r="52" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
       <c r="B52" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C52" s="4"/>
       <c r="D52" s="17"/>
@@ -2872,10 +2877,10 @@
       <c r="G52" s="17"/>
       <c r="H52" s="17"/>
       <c r="I52" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J52" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K52" s="17"/>
       <c r="L52" s="17"/>
@@ -2914,7 +2919,7 @@
       <c r="H53" s="17"/>
       <c r="I53" s="4"/>
       <c r="J53" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="17"/>
@@ -2945,7 +2950,7 @@
     <row r="54" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
       <c r="B54" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="17"/>
@@ -2954,10 +2959,10 @@
       <c r="G54" s="17"/>
       <c r="H54" s="17"/>
       <c r="I54" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J54" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="17"/>
@@ -2996,7 +3001,7 @@
       <c r="H55" s="17"/>
       <c r="I55" s="4"/>
       <c r="J55" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
@@ -3027,7 +3032,7 @@
     <row r="56" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
       <c r="B56" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="17"/>
@@ -3036,10 +3041,10 @@
       <c r="G56" s="17"/>
       <c r="H56" s="17"/>
       <c r="I56" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J56" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="17"/>
@@ -3107,7 +3112,7 @@
     <row r="58" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
       <c r="B58" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C58" s="17"/>
       <c r="D58" s="17"/>
@@ -3139,7 +3144,7 @@
       <c r="AD58" s="12"/>
       <c r="AE58" s="4"/>
       <c r="AF58" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG58" s="16"/>
       <c r="AH58" s="16"/>
@@ -3149,28 +3154,28 @@
       <c r="A59" s="5"/>
       <c r="B59" s="17"/>
       <c r="C59" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D59" s="17"/>
       <c r="E59" s="4"/>
       <c r="F59" s="17"/>
       <c r="G59" s="4"/>
       <c r="H59" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I59" s="4"/>
       <c r="J59" s="17"/>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N59" s="4"/>
       <c r="O59" s="10"/>
       <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
       <c r="R59" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S59" s="4"/>
       <c r="T59" s="4"/>
@@ -3232,7 +3237,7 @@
     <row r="61" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C61" s="17"/>
       <c r="D61" s="17"/>
@@ -3264,7 +3269,7 @@
       <c r="AD61" s="12"/>
       <c r="AE61" s="4"/>
       <c r="AF61" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG61" s="16"/>
       <c r="AH61" s="16"/>
@@ -3273,7 +3278,7 @@
     <row r="62" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
       <c r="B62" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C62" s="17"/>
       <c r="D62" s="17"/>
@@ -3315,7 +3320,7 @@
       <c r="A63" s="5"/>
       <c r="B63" s="17"/>
       <c r="C63" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D63" s="17"/>
       <c r="E63" s="17"/>
@@ -3327,7 +3332,7 @@
       <c r="K63" s="17"/>
       <c r="L63" s="17"/>
       <c r="M63" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
@@ -3356,7 +3361,7 @@
       <c r="A64" s="5"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D64" s="17"/>
       <c r="E64" s="17"/>
@@ -3368,7 +3373,7 @@
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
       <c r="M64" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
@@ -3433,7 +3438,7 @@
     <row r="66" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
       <c r="B66" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C66" s="17"/>
       <c r="D66" s="17"/>
@@ -3465,7 +3470,7 @@
       <c r="AD66" s="12"/>
       <c r="AE66" s="4"/>
       <c r="AF66" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG66" s="16"/>
       <c r="AH66" s="16"/>
@@ -3551,28 +3556,28 @@
       <c r="A69" s="5"/>
       <c r="B69" s="17"/>
       <c r="C69" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D69" s="17"/>
       <c r="E69" s="4"/>
       <c r="F69" s="17"/>
       <c r="G69" s="4"/>
       <c r="H69" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I69" s="4"/>
       <c r="J69" s="24"/>
       <c r="K69" s="24"/>
       <c r="L69" s="24"/>
       <c r="M69" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
       <c r="P69" s="4"/>
       <c r="Q69" s="4"/>
       <c r="R69" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S69" s="4"/>
       <c r="T69" s="4"/>
@@ -3632,7 +3637,7 @@
     <row r="71" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
       <c r="B71" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" s="17"/>
       <c r="D71" s="17"/>
@@ -3664,7 +3669,7 @@
       <c r="AD71" s="12"/>
       <c r="AE71" s="4"/>
       <c r="AF71" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG71" s="16"/>
       <c r="AH71" s="16"/>
@@ -3673,13 +3678,13 @@
     <row r="72" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
       <c r="B72" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C72" s="15"/>
       <c r="D72" s="15"/>
       <c r="E72" s="15"/>
       <c r="F72" s="25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G72" s="25"/>
       <c r="H72" s="25"/>
@@ -3689,7 +3694,7 @@
       <c r="L72" s="25"/>
       <c r="M72" s="25"/>
       <c r="N72" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O72" s="25"/>
       <c r="P72" s="25"/>
@@ -3699,7 +3704,7 @@
       <c r="T72" s="25"/>
       <c r="U72" s="25"/>
       <c r="V72" s="25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W72" s="25"/>
       <c r="X72" s="25"/>
@@ -3711,7 +3716,7 @@
       <c r="AD72" s="12"/>
       <c r="AE72" s="4"/>
       <c r="AF72" s="26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AG72" s="26"/>
       <c r="AH72" s="26"/>
@@ -3720,7 +3725,7 @@
     <row r="73" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
       <c r="B73" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15"/>
@@ -3870,13 +3875,13 @@
     <row r="77" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
       <c r="B77" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15"/>
       <c r="E77" s="15"/>
       <c r="F77" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G77" s="15"/>
       <c r="H77" s="15"/>
@@ -3886,7 +3891,7 @@
       <c r="L77" s="15"/>
       <c r="M77" s="15"/>
       <c r="N77" s="15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O77" s="15"/>
       <c r="P77" s="15"/>
@@ -3896,7 +3901,7 @@
       <c r="T77" s="15"/>
       <c r="U77" s="15"/>
       <c r="V77" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W77" s="15"/>
       <c r="X77" s="15"/>
@@ -3952,13 +3957,13 @@
     <row r="79" ht="19.9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
       <c r="B79" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="15"/>
       <c r="E79" s="15"/>
       <c r="F79" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G79" s="15"/>
       <c r="H79" s="15"/>
@@ -3968,7 +3973,7 @@
       <c r="L79" s="15"/>
       <c r="M79" s="15"/>
       <c r="N79" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O79" s="27"/>
       <c r="P79" s="27"/>
@@ -3978,7 +3983,7 @@
       <c r="T79" s="27"/>
       <c r="U79" s="27"/>
       <c r="V79" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W79" s="15"/>
       <c r="X79" s="15"/>
